--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249369억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 249397억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257519억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 257574억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257091억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 257854억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255889억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 256663억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253645억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 254403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 250825억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 251568억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 246344억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 246390억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239108억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239153억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 230680억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 230726억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -924,13 +924,13 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 600억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 601억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 672억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 673억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
@@ -942,7 +942,7 @@
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 836억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 837억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1863,55 +1863,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249369억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 249397억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257519억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 257574억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257091억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 257854억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255889억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 256663억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253645억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 254403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 250825억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 251568억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 246344억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 246390억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239108억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239153억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 230680억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 230726억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2348,13 +2348,13 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 600억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 601억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 672억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 673억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -2366,7 +2366,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 836억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 837억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4647,7 +4647,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.6, "op_wape_pct": 29.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 544.1, "rev_act": 528.22, "op_pred": 59.42, "op_act": 64.08}, {"q": "2025Q4", "rev_pred": 608.1, "rev_act": 518.55, "op_pred": 66.41, "op_act": 34.35}, {"q": "2026Q1", "rev_pred": 513.87, "rev_act": 564.46, "op_pred": 56.12, "op_act": 79.81}, {"q": "2026Q2", "rev_pred": 631.07, "rev_act": 596.77, "op_pred": 68.92, "op_act": 88.19}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.6, "op_wape_pct": 29.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 544.1, "rev_act": 528.22, "op_pred": 59.42, "op_act": 64.08}, {"q": "2025Q4", "rev_pred": 608.1, "rev_act": 518.55, "op_pred": 66.41, "op_act": 34.35}, {"q": "2026Q1", "rev_pred": 513.87, "rev_act": 564.46, "op_pred": 56.12, "op_act": 79.81}, {"q": "2026Q2", "rev_pred": 631.06, "rev_act": 596.77, "op_pred": 68.92, "op_act": 88.19}]}</t>
         </is>
       </c>
     </row>
@@ -6698,33 +6698,33 @@
         <v>0.243843</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.415694</v>
+        <v>0.415849</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.107964</v>
+        <v>0.108194</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.244435</v>
+        <v>0.248121</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.06674099999999999</v>
+        <v>0.069967</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.01715</v>
+        <v>0.020077</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.025999</v>
+        <v>-0.023324</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.041797</v>
+        <v>-0.044452</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.065576</v>
+        <v>-0.06822300000000001</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.090545</v>
+        <v>-0.093066</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6844,39 +6844,39 @@
         <v>0.056193</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.05619</v>
+        <v>0.056184</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.056188</v>
+        <v>0.056192</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.056191</v>
+        <v>0.056187</v>
       </c>
       <c r="AH22" s="24" t="n">
+        <v>0.056189</v>
+      </c>
+      <c r="AI22" s="24" t="n">
         <v>0.056187</v>
-      </c>
-      <c r="AI22" s="24" t="n">
-        <v>0.056194</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.056194</v>
+        <v>0.056192</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.056183</v>
+        <v>0.056187</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.056191</v>
+        <v>0.056196</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.056193</v>
+        <v>0.056196</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6999,39 +6999,39 @@
         <v>0.131351</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131343</v>
+        <v>0.131342</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.13134</v>
+        <v>0.131345</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131342</v>
+        <v>0.131344</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131351</v>
+        <v>0.131339</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131351</v>
+        <v>0.131347</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131349</v>
+        <v>0.131355</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131352</v>
+        <v>0.131342</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131346</v>
+        <v>0.131353</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131352</v>
+        <v>0.13134</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7283,29 +7283,29 @@
         <v>6.04</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>7.49</v>
+        <v>7.5</v>
       </c>
       <c r="AH25" s="29" t="n">
         <v>9.24</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>12.72</v>
+        <v>12.74</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>14.25</v>
+        <v>14.27</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>16.04</v>
+        <v>16.06</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>17.73</v>
+        <v>17.75</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7738,39 +7738,39 @@
         <v>0.196015</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.196078</v>
+        <v>0.196058</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE15/subQ!AE14,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.196108</v>
+        <v>0.196085</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.196065</v>
+        <v>0.196096</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.196098</v>
+        <v>0.196049</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.196117</v>
+        <v>0.19611</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.196105</v>
+        <v>0.196094</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.196108</v>
+        <v>0.196034</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.196108</v>
+        <v>0.196029</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.19606</v>
+        <v>0.19608</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8264,13 +8264,13 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AH32" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AH32" s="29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AI32" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
@@ -8392,13 +8392,13 @@
         <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AH33" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI33" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AH33" s="29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AI33" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
@@ -8641,33 +8641,33 @@
         <v>-0.6027709999999999</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>-1.721408</v>
+        <v>-1.721627</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>2.078812</v>
+        <v>2.078485</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.808605</v>
+        <v>0.81071</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.430702</v>
+        <v>0.431367</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.324557</v>
+        <v>0.324915</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.207515</v>
+        <v>0.207654</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.200495</v>
+        <v>0.200147</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.158014</v>
+        <v>0.15775</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.143143</v>
+        <v>0.142952</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8769,33 +8769,33 @@
         <v>0.507404</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.381772</v>
+        <v>0.381821</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.240733</v>
+        <v>0.240795</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.23236</v>
+        <v>0.232991</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.181639</v>
+        <v>0.182058</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.165744</v>
+        <v>0.166052</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.120379</v>
+        <v>0.120566</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.125385</v>
+        <v>0.125256</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.105388</v>
+        <v>0.105294</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.100028</v>
+        <v>0.09994500000000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9431,23 +9431,23 @@
         <v>-0.539256</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.302476</v>
+        <v>-0.303552</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.139756</v>
+        <v>-0.141113</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.126741</v>
+        <v>-0.128134</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.068759</v>
+        <v>-0.070254</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.040123</v>
+        <v>-0.040185</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.014196</v>
+        <v>-0.012638</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9841,39 +9841,39 @@
         <v>0.131351</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>0.131343</v>
+        <v>0.131342</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE35,"")</f>
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.13134</v>
+        <v>0.131345</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.131342</v>
+        <v>0.131344</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.131351</v>
+        <v>0.131339</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.131351</v>
+        <v>0.131347</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.131349</v>
+        <v>0.131355</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.131352</v>
+        <v>0.131342</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.131346</v>
+        <v>0.131353</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.131352</v>
+        <v>0.13134</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -40320,7 +40320,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>656.1</v>
+        <v>656.6</v>
       </c>
     </row>
     <row r="30">
@@ -40360,7 +40360,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2158</v>
+        <v>0.2159</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239878억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239825억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249397억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 250208억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257574억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 261772억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257854억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 269220억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 256663억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 279952억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 293972억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 251568억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 310408억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 246390억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326143억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239153억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 340120억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 230726억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 351874억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -906,43 +906,43 @@
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 353억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 355억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 436억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 441억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 515억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 527억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 601억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 625억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 673억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 713억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 757억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 822억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 837억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 932억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1857,61 +1857,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239878억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239825억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249397억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 250208억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257574억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261772억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257854억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 269220억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 256663억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279952억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 293972억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 251568억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 310408억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 246390억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326143억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239153억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 340120억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 230726억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 351874억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2330,43 +2330,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 353억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 355억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 436억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 441억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 515억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 527억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 601억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 625억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 673억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 713억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 757억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 822억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 837억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 932억 × 8.48% − 총차입금 250억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4519,7 +4519,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.6, "op_wape_pct": 29.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 544.1, "rev_act": 528.22, "op_pred": 59.42, "op_act": 64.08}, {"q": "2025Q4", "rev_pred": 608.1, "rev_act": 518.55, "op_pred": 66.41, "op_act": 34.35}, {"q": "2026Q1", "rev_pred": 513.87, "rev_act": 564.46, "op_pred": 56.12, "op_act": 79.81}, {"q": "2026Q2", "rev_pred": 631.06, "rev_act": 596.77, "op_pred": 68.92, "op_act": 88.19}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.6, "op_wape_pct": 29.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 10.7, "wape_trend": 13.2, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 544.1, "rev_act": 528.22, "op_pred": 59.42, "op_act": 64.08}, {"q": "2025Q4", "rev_pred": 608.1, "rev_act": 518.55, "op_pred": 66.41, "op_act": 34.35}, {"q": "2026Q1", "rev_pred": 513.87, "rev_act": 564.46, "op_pred": 56.12, "op_act": 79.81}, {"q": "2026Q2", "rev_pred": 631.06, "rev_act": 596.77, "op_pred": 68.92, "op_act": 88.19}]}</t>
         </is>
       </c>
     </row>
@@ -6695,36 +6695,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.243843</v>
+        <v>0.243559</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.415849</v>
+        <v>0.420458</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.108194</v>
+        <v>0.126264</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.248121</v>
+        <v>0.303151</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.069967</v>
+        <v>0.167324</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.020077</v>
+        <v>0.174903</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.023324</v>
+        <v>0.185786</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.044452</v>
+        <v>0.211437</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.06822300000000001</v>
+        <v>0.214912</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.093066</v>
+        <v>0.19697</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6841,26 +6841,26 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.056193</v>
+        <v>0.056191</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.056184</v>
+        <v>0.056192</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.056192</v>
+        <v>0.056187</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.056187</v>
+        <v>0.056193</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.056189</v>
+        <v>0.056183</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.056187</v>
+        <v>0.056193</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
@@ -6870,13 +6870,13 @@
         <v>0.056192</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.056187</v>
+        <v>0.056193</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.056196</v>
+        <v>0.056185</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.056196</v>
+        <v>0.056185</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6996,10 +6996,10 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.131351</v>
+        <v>0.13135</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131342</v>
+        <v>0.13135</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -7009,29 +7009,29 @@
         <v>0.131345</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131344</v>
+        <v>0.131339</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131339</v>
+        <v>0.131341</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131347</v>
+        <v>0.131348</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131355</v>
+        <v>0.131341</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131342</v>
+        <v>0.131343</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131353</v>
+        <v>0.131348</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.13134</v>
+        <v>0.131349</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7280,32 +7280,32 @@
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>9.24</v>
+        <v>9.34</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>10.92</v>
+        <v>11.17</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>12.74</v>
+        <v>13.25</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>14.27</v>
+        <v>15.11</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>16.06</v>
+        <v>17.43</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>17.75</v>
+        <v>19.77</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7735,42 +7735,42 @@
         <v/>
       </c>
       <c r="AC28" s="24" t="n">
-        <v>0.196015</v>
+        <v>0.19606</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.196058</v>
+        <v>0.19605</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE15/subQ!AE14,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.196085</v>
+        <v>0.196031</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.196096</v>
+        <v>0.196086</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.196049</v>
+        <v>0.196119</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.19611</v>
+        <v>0.196048</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.196094</v>
+        <v>0.196087</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.196034</v>
+        <v>0.196058</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.196029</v>
+        <v>0.196114</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.19608</v>
+        <v>0.196077</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8264,13 +8264,13 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH32" s="29" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH32" s="29" t="n">
+      <c r="AI32" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AI32" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
@@ -8280,10 +8280,10 @@
         <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8392,13 +8392,13 @@
         <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH33" s="29" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH33" s="29" t="n">
+      <c r="AI33" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AI33" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="AM33" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AN33" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8638,36 +8638,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>-0.6027709999999999</v>
+        <v>-0.602684</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>-1.721627</v>
+        <v>-1.726498</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>2.078485</v>
+        <v>2.0969</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.81071</v>
+        <v>0.834224</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.431367</v>
+        <v>0.456453</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.324915</v>
+        <v>0.356649</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.207654</v>
+        <v>0.235783</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.200147</v>
+        <v>0.237183</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.15775</v>
+        <v>0.193027</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.142952</v>
+        <v>0.180729</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8766,36 +8766,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>0.507404</v>
+        <v>0.507257</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.381821</v>
+        <v>0.383119</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.240795</v>
+        <v>0.244345</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.232991</v>
+        <v>0.241967</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.182058</v>
+        <v>0.195552</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.166052</v>
+        <v>0.186117</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.120566</v>
+        <v>0.140733</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.125256</v>
+        <v>0.153351</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.105294</v>
+        <v>0.133886</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.09994500000000001</v>
+        <v>0.131904</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9418,36 +9418,36 @@
         <v/>
       </c>
       <c r="AC42" s="24" t="n">
-        <v>-0.270228</v>
+        <v>-0.269442</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.613326</v>
+        <v>-0.613851</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.57414</v>
+        <v>-0.575919</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.539256</v>
+        <v>-0.546832</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.303552</v>
+        <v>-0.330108</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.141113</v>
+        <v>-0.201087</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.128134</v>
+        <v>-0.21958</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.070254</v>
+        <v>-0.203647</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.040185</v>
+        <v>-0.208668</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.012638</v>
+        <v>-0.209184</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9547,26 +9547,26 @@
         <v>-0.535316</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>-0.443925</v>
+        <v>-0.448598</v>
       </c>
       <c r="AH43" s="24" t="n">
         <v>-0.175182</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>-0.169231</v>
+        <v>-0.176923</v>
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>-0.168</v>
+        <v>-0.184</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.159664</v>
+        <v>-0.177966</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.150442</v>
+        <v>-0.185841</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.148148</v>
+        <v>-0.186916</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -9838,10 +9838,10 @@
         <v/>
       </c>
       <c r="AC45" s="24" t="n">
-        <v>0.131351</v>
+        <v>0.13135</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>0.131342</v>
+        <v>0.13135</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE35,"")</f>
@@ -9851,29 +9851,29 @@
         <v>0.131345</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.131344</v>
+        <v>0.131339</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.131339</v>
+        <v>0.131341</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.131347</v>
+        <v>0.131348</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.131355</v>
+        <v>0.131341</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.131342</v>
+        <v>0.131343</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.131353</v>
+        <v>0.131348</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.13134</v>
+        <v>0.131349</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40320,7 +40320,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>656.6</v>
+        <v>667.2</v>
       </c>
     </row>
     <row r="30">
@@ -40340,7 +40340,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.69</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="32">
@@ -40360,7 +40360,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2159</v>
+        <v>0.2194</v>
       </c>
     </row>
     <row r="34">
@@ -40370,7 +40370,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="35">
@@ -40380,7 +40380,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7300</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248423억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 248403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258809억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 258767억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 265067억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 265003억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275213억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 275126억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289200억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289112억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 305627억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 305542억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 321366억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 321284억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 335348억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 335270억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 347110억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 347037억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248423억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258809억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 258767억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 265067억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265003억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275213억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 275126억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289200억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289112억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 305627억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 305542억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 321366억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 321284억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 335348억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 335270억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 347110억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 347037억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4590</v>
+        <v>4585</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4537.5</v>
+        <v>4553.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.240359799</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.410313967</v>
+        <v>0.410217545</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.113508687</v>
+        <v>0.113331526</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.283042732</v>
+        <v>0.282724351</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.15052352</v>
+        <v>0.150157209</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.164155226</v>
+        <v>0.163879279</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180898286</v>
+        <v>0.180752033</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.212399436</v>
+        <v>0.212386837</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.218492969</v>
+        <v>0.218602367</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.200230217</v>
+        <v>0.200350131</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131353216</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131351529</v>
+        <v>0.131346835</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131354112</v>
+        <v>0.131343189</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131347299</v>
+        <v>0.13134071</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131347838</v>
+        <v>0.131349859</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.13134125</v>
+        <v>0.131346124</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131347426</v>
+        <v>0.131344169</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.13134621</v>
+        <v>0.131347851</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131344584</v>
+        <v>0.131341951</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131351288</v>
+        <v>0.131348923</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.005606275</v>
+        <v>0.004687776</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.008337078</v>
+        <v>-0.007197651</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.008295912000000001</v>
+        <v>-0.008401774000000001</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.011181375</v>
+        <v>-0.006010093</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.006809397</v>
+        <v>0.001977172</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.006377216</v>
+        <v>-0.00145276</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.005065187</v>
+        <v>-0.010005269</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.0008242189999999999</v>
+        <v>0.005662383</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.004516325</v>
+        <v>-0.009743893999999999</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.003636207</v>
+        <v>0.000945603</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.005606275</v>
+        <v>0.004687776</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.008337078</v>
+        <v>-0.007197651</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.008295912000000001</v>
+        <v>-0.008401774000000001</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.011181375</v>
+        <v>-0.006010093</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.006809397</v>
+        <v>0.001977172</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.006377216</v>
+        <v>-0.00145276</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.005065187</v>
+        <v>-0.010005269</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>0.0008242189999999999</v>
+        <v>0.005662383</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.004516325</v>
+        <v>-0.009743893999999999</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.003636207</v>
+        <v>0.000945603</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8841,33 +8841,33 @@
         <v>-0.577145716</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-1.546425637</v>
+        <v>-1.546220214</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.454887218</v>
+        <v>2.455810455</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.876605005</v>
+        <v>0.8764827509999999</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.465383277</v>
+        <v>0.465290263</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.362100348</v>
+        <v>0.362067601</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.235511141</v>
+        <v>0.235514616</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.239054785</v>
+        <v>0.239046074</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193255783</v>
+        <v>0.193269176</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.181231215</v>
+        <v>0.181229619</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8969,33 +8969,33 @@
         <v>0.485834779</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.370386773</v>
+        <v>0.370337565</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.234514704</v>
+        <v>0.234487216</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.23432228</v>
+        <v>0.234277736</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189131869</v>
+        <v>0.189078997</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181344378</v>
+        <v>0.181329898</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135977052</v>
+        <v>0.135964029</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150149884</v>
+        <v>0.15012997</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.130753528</v>
+        <v>0.13073851</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.129384247</v>
+        <v>0.129397869</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4590</v>
+        <v>4585</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960773289102546</v>
+        <v>0.1960857828434313</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05619025705410691</v>
+        <v>0.05618726587075754</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05880487019539181</v>
+        <v>0.0588190947633298</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04059367867583755</v>
+        <v>0.04060583435696826</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>631.5</v>
+        <v>631.3</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="32">
@@ -41998,7 +41998,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2077</v>
+        <v>0.2076</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 248386억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258767억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 258722억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 265003억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 264931억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275126억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 275028억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289112억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289006억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 305542억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 305439억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 321284억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 321185억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 335270억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 335176억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 347037억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 346949억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248403억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248386억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258767억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 258722억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 265003억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264931억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275126억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 275028억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289112억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289006억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 305542억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 305439억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 321284억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 321185억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 335270억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 335176억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 347037억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 346949억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2154,7 +2154,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 505억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 504억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2178,7 +2178,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 881억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 880억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2214,7 +2214,7 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 505억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 504억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2238,7 +2238,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 881억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 880억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4585</v>
+        <v>4490</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4390</v>
+        <v>4360</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4553.3</v>
+        <v>4535</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.240359799</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.410217545</v>
+        <v>0.410121122</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.113331526</v>
+        <v>0.113136649</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.282724351</v>
+        <v>0.282389213</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.150157209</v>
+        <v>0.149745108</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.163879279</v>
+        <v>0.163521238</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180752033</v>
+        <v>0.180560861</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.212386837</v>
+        <v>0.21232474</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.218602367</v>
+        <v>0.218693996</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.200350131</v>
+        <v>0.20049601</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131353216</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131346835</v>
+        <v>0.131342141</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131343189</v>
+        <v>0.131350267</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.13134071</v>
+        <v>0.1313489</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131349859</v>
+        <v>0.131343838</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131346124</v>
+        <v>0.131348511</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131344169</v>
+        <v>0.131347992</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131347851</v>
+        <v>0.131345793</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131341951</v>
+        <v>0.13134647</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131348923</v>
+        <v>0.131343196</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004687776</v>
+        <v>0.004990651</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007197651</v>
+        <v>-0.014708745</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.008401774000000001</v>
+        <v>0.004085883</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.006010093</v>
+        <v>-0.001492675</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.001977172</v>
+        <v>0.000312006</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00145276</v>
+        <v>-0.003074955</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.010005269</v>
+        <v>-0.00415874</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.005662383</v>
+        <v>0.003633887</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.009743893999999999</v>
+        <v>-0.003914239</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.000945603</v>
+        <v>-0.001291564</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.004687776</v>
+        <v>0.004990651</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007197651</v>
+        <v>-0.014708745</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.008401774000000001</v>
+        <v>0.004085883</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.006010093</v>
+        <v>-0.001492675</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.001977172</v>
+        <v>0.000312006</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.00145276</v>
+        <v>-0.003074955</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.010005269</v>
+        <v>-0.00415874</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>0.005662383</v>
+        <v>0.003633887</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.009743893999999999</v>
+        <v>-0.003914239</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.000945603</v>
+        <v>-0.001291564</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8841,33 +8841,33 @@
         <v>-0.577145716</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-1.546220214</v>
+        <v>-1.54601479</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.455810455</v>
+        <v>2.456358164</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.8764827509999999</v>
+        <v>0.876455862</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.465290263</v>
+        <v>0.465224201</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.362067601</v>
+        <v>0.362049171</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.235514616</v>
+        <v>0.235495873</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.239046074</v>
+        <v>0.239048605</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193269176</v>
+        <v>0.193270929</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.181229619</v>
+        <v>0.181236674</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8973,29 +8973,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.234487216</v>
+        <v>0.234415398</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.234277736</v>
+        <v>0.234233186</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189078997</v>
+        <v>0.189049684</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181329898</v>
+        <v>0.181252354</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135964029</v>
+        <v>0.135955565</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.15012997</v>
+        <v>0.150114484</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.13073851</v>
+        <v>0.130726845</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.129397869</v>
+        <v>0.129391719</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4585</v>
+        <v>4490</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,590원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960857828434313</v>
+        <v>0.196075490094972</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618726587075754</v>
+        <v>0.05618888432936654</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0588190947633298</v>
+        <v>0.05882749414775901</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04060583435696826</v>
+        <v>0.04062133315992117</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>631.3</v>
+        <v>631.2</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.26</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="32">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239209억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239093억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248386억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 248064억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258722억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 258383억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264931억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 264852억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275028억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 275677억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289006억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 290882억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 305439억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 308797억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 321185억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326204억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 335176억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 341945억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 346949억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 355476억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1764,61 +1764,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239209억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239093억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248386억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248064억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258722억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 258383억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264931억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264852억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275028억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 275677억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289006억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 290882억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 305439억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 308797억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 321185억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326204억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 335176억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 341945억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 346949억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355476억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,19 +2166,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 677억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 678억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 779억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 781억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 880억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 885억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,19 +2226,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 677억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 678억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 779억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 781억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 880억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 885억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6638,36 +6638,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.240359799</v>
+        <v>0.239772919</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.410121122</v>
+        <v>0.408289095</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.113136649</v>
+        <v>0.111683931</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.282389213</v>
+        <v>0.282003804</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.149745108</v>
+        <v>0.153007467</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.163521238</v>
+        <v>0.172607392</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180560861</v>
+        <v>0.19510757</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.21232474</v>
+        <v>0.231641963</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.218693996</v>
+        <v>0.240375065</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.20049601</v>
+        <v>0.222054839</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6949,42 +6949,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.131353216</v>
+        <v>0.131339044</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131342141</v>
+        <v>0.131348679</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131350267</v>
+        <v>0.131346614</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.1313489</v>
+        <v>0.131349175</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131343838</v>
+        <v>0.13135206</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131348511</v>
+        <v>0.131341087</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131347992</v>
+        <v>0.131345592</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131345793</v>
+        <v>0.131341003</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.13134647</v>
+        <v>0.131351634</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131343196</v>
+        <v>0.131346336</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004990651</v>
+        <v>-0.004617304</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.014708745</v>
+        <v>-0.001206232</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.004085883</v>
+        <v>-0.005731668</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.001492675</v>
+        <v>0.001924198</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.000312006</v>
+        <v>0.000252619</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.003074955</v>
+        <v>-0.005293212</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.00415874</v>
+        <v>0.001756145</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.003633887</v>
+        <v>-0.013072844</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.003914239</v>
+        <v>0.001474024</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.001291564</v>
+        <v>-0.001103916</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.004990651</v>
+        <v>-0.004617304</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.014708745</v>
+        <v>-0.001206232</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.004085883</v>
+        <v>-0.005731668</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.001492675</v>
+        <v>0.001924198</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.000312006</v>
+        <v>0.000252619</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.003074955</v>
+        <v>-0.005293212</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.00415874</v>
+        <v>0.001756145</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>0.003633887</v>
+        <v>-0.013072844</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.003914239</v>
+        <v>0.001474024</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.001291564</v>
+        <v>-0.001103916</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8838,36 +8838,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>-0.577145716</v>
+        <v>-0.576885124</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-1.54601479</v>
+        <v>-1.543009649</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.456358164</v>
+        <v>2.465028355</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.876455862</v>
+        <v>0.878232406</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.465224201</v>
+        <v>0.467003602</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.362049171</v>
+        <v>0.364431949</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.235495873</v>
+        <v>0.237636406</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.239048605</v>
+        <v>0.241933215</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193270929</v>
+        <v>0.195936633</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.181236674</v>
+        <v>0.184123275</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8966,36 +8966,36 @@
         <v/>
       </c>
       <c r="AC37" s="24" t="n">
-        <v>0.485834779</v>
+        <v>0.48554232</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.370337565</v>
+        <v>0.369918299</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.234415398</v>
+        <v>0.234245886</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.234233186</v>
+        <v>0.234295861</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189049684</v>
+        <v>0.189585643</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181252354</v>
+        <v>0.182447167</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135955565</v>
+        <v>0.137295666</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150114484</v>
+        <v>0.152077129</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.130726845</v>
+        <v>0.132795905</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.129391719</v>
+        <v>0.131721037</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.196075490094972</v>
+        <v>0.1960747871984537</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618888432936654</v>
+        <v>0.0561918272295067</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05882749414775901</v>
+        <v>0.05881629811603584</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04062133315992117</v>
+        <v>0.04060464966321794</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>631.2</v>
+        <v>630.6</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.11</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="32">
@@ -41998,7 +41998,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2076</v>
+        <v>0.2074</v>
       </c>
     </row>
     <row r="34">
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="35">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248064억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 248054억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258383억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 258373억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264852억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 264841억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275677억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 275666억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 290882억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 290881억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 308797억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 308795억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326204억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326202억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 341945억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 341944억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355476억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 355475억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248064억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248054억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258383억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 258373억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264852억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264841억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275677억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 275666억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 290882억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 290881억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 308797억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 308795억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326204억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326202억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 341945억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 341944억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355476억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355475억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4490</v>
+        <v>4370</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4360</v>
+        <v>4325</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4535</v>
+        <v>4501</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.239772919</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.408289095</v>
+        <v>0.408231241</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.111683931</v>
+        <v>0.111630783</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.282003804</v>
+        <v>0.281953533</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153007467</v>
+        <v>0.152961657</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.172607392</v>
+        <v>0.172641871</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.19510757</v>
+        <v>0.195164709</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.231641963</v>
+        <v>0.231690261</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.240375065</v>
+        <v>0.240424348</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.222054839</v>
+        <v>0.22206911</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,23 +6952,23 @@
         <v>0.131339044</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131348679</v>
+        <v>0.131340381</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131346614</v>
+        <v>0.131352893</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131349175</v>
+        <v>0.131341255</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.13135206</v>
+        <v>0.131344035</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131341087</v>
+        <v>0.131342621</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
@@ -6981,7 +6981,7 @@
         <v>0.131341003</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131351634</v>
+        <v>0.131340957</v>
       </c>
       <c r="AN23" s="24" t="n">
         <v>0.131346336</v>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.004617304</v>
+        <v>-0.005075702</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001206232</v>
+        <v>-0.009739380000000001</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005731668</v>
+        <v>0.003868894</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.001924198</v>
+        <v>-0.006712352</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.000252619</v>
+        <v>-0.008354314999999999</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.005293212</v>
+        <v>-0.005911196</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001756145</v>
+        <v>0.001240276</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.013072844</v>
+        <v>-0.003822018</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.001474024</v>
+        <v>-0.007281158</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.001103916</v>
+        <v>-0.001869921</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.004617304</v>
+        <v>-0.005075702</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001206232</v>
+        <v>-0.009739380000000001</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.005731668</v>
+        <v>0.003868894</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>0.001924198</v>
+        <v>-0.006712352</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.000252619</v>
+        <v>-0.008354314999999999</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.005293212</v>
+        <v>-0.005911196</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.001756145</v>
+        <v>0.001240276</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.013072844</v>
+        <v>-0.003822018</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.001474024</v>
+        <v>-0.007281158</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.001103916</v>
+        <v>-0.001869921</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8845,29 +8845,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.465028355</v>
+        <v>2.464650284</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.878232406</v>
+        <v>0.878328241</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.467003602</v>
+        <v>0.467030733</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.364431949</v>
+        <v>0.36440678</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.237636406</v>
+        <v>0.237679224</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.241933215</v>
+        <v>0.241915437</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.195936633</v>
+        <v>0.195962915</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.184123275</v>
+        <v>0.184110394</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8973,29 +8973,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.234245886</v>
+        <v>0.234209959</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.234295861</v>
+        <v>0.234302681</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189585643</v>
+        <v>0.189590114</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.182447167</v>
+        <v>0.182450784</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.137295666</v>
+        <v>0.137281202</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.152077129</v>
+        <v>0.152081613</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.132795905</v>
+        <v>0.132799304</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.131721037</v>
+        <v>0.131724013</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4490</v>
+        <v>4370</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,590원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,565원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960747871984537</v>
+        <v>0.1960802535103941</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0561918272295067</v>
+        <v>0.05619149302907538</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05881629811603584</v>
+        <v>0.05881809460062299</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04060464966321794</v>
+        <v>0.0406057690782046</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.12</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="32">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239093억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239820억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248054억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 249926억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258373억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 260670억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264841억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267024억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275666억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 276616억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 290881억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289919억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 308795억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 306502억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326202억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 323124억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 341944억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 338635억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355475억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 352477억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1764,61 +1764,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239093억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239820억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248054억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 249926억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258373억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 260670억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264841억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267024억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275666억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276616억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 290881억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289919억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 308795억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 306502억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326202억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 323124억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 341944억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 338635억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355475억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352477억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2136,43 +2136,43 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 278억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 279억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 344억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 345억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 424억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 426억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 504억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 507억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 596억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 599억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 678억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 680억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 781억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 782억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2196,43 +2196,43 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 278억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 279억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 344억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 345억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 424억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 426억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 504억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 507억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 596억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 599억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 678억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 680억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 781억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 782억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -6638,36 +6638,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.239772919</v>
+        <v>0.243540305</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.408231241</v>
+        <v>0.418857</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.111630783</v>
+        <v>0.121516355</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.281953533</v>
+        <v>0.292510384</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.152961657</v>
+        <v>0.15342691</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.172641871</v>
+        <v>0.160013592</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.195164709</v>
+        <v>0.175831293</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.231690261</v>
+        <v>0.21009166</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.240424348</v>
+        <v>0.224209387</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.22206911</v>
+        <v>0.215775414</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6949,42 +6949,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.131339044</v>
+        <v>0.131352191</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131340381</v>
+        <v>0.131348964</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131352893</v>
+        <v>0.131348235</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131341255</v>
+        <v>0.131344561</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131344035</v>
+        <v>0.131342062</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131342621</v>
+        <v>0.131344613</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131345592</v>
+        <v>0.131347735</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131341003</v>
+        <v>0.131350575</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131340957</v>
+        <v>0.131340902</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131346336</v>
+        <v>0.131346132</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.005075702</v>
+        <v>0.001230305</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.009739380000000001</v>
+        <v>-0.001236555</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.003868894</v>
+        <v>-0.000805338</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.006712352</v>
+        <v>-0.013973955</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.008354314999999999</v>
+        <v>-0.00163545</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.005911196</v>
+        <v>-0.006653814</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001240276</v>
+        <v>-0.002285036</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.003822018</v>
+        <v>0.000262706</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.007281158</v>
+        <v>-0.008358809</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.001869921</v>
+        <v>-0.010199848</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.005075702</v>
+        <v>0.001230305</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.009739380000000001</v>
+        <v>-0.001236555</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.003868894</v>
+        <v>-0.000805338</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.006712352</v>
+        <v>-0.013973955</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.008354314999999999</v>
+        <v>-0.00163545</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.005911196</v>
+        <v>-0.006653814</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.001240276</v>
+        <v>-0.002285036</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.003822018</v>
+        <v>0.000262706</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.007281158</v>
+        <v>-0.008358809</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.001869921</v>
+        <v>-0.010199848</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8838,36 +8838,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>-0.576885124</v>
+        <v>-0.578709269</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-1.543009649</v>
+        <v>-1.561649485</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.464650284</v>
+        <v>2.415198238</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.878328241</v>
+        <v>0.872514243</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.467030733</v>
+        <v>0.463203215</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.36440678</v>
+        <v>0.359998431</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.237679224</v>
+        <v>0.234588201</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.241915437</v>
+        <v>0.23889525</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.195962915</v>
+        <v>0.193942023</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.184110394</v>
+        <v>0.182721471</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8966,36 +8966,36 @@
         <v/>
       </c>
       <c r="AC37" s="24" t="n">
-        <v>0.48554232</v>
+        <v>0.487077727</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.369918299</v>
+        <v>0.37243719</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.234209959</v>
+        <v>0.235688185</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.234302681</v>
+        <v>0.235323109</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189590114</v>
+        <v>0.189345224</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.182450784</v>
+        <v>0.181064762</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.137281202</v>
+        <v>0.135863936</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.152081613</v>
+        <v>0.150383903</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.132799304</v>
+        <v>0.13147935</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.131724013</v>
+        <v>0.130722204</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960802535103941</v>
+        <v>0.1960782488925288</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05619149302907538</v>
+        <v>0.05618929325549621</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05881809460062299</v>
+        <v>0.05880976863799442</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.0406057690782046</v>
+        <v>0.04061950044634533</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>630.6</v>
+        <v>635.2</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.93</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="32">
@@ -41998,7 +41998,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2074</v>
+        <v>0.2089</v>
       </c>
     </row>
     <row r="34">
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="35">
@@ -42018,7 +42018,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7000</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249926억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 249923억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 260670억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 260694억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267024억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267074억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276616억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 276691억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289919억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 290022억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 306502억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 306602억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 323124억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 323220억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 338635억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 338726억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352477억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 352563억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249926억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 249923억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 260670억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 260694억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267024억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267074억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276616억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276691억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289919억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 290022억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 306502억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 306602억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 323124억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 323220억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 338635억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 338726억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352477억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352563억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4370</v>
+        <v>4300</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4325</v>
+        <v>4255</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4501</v>
+        <v>4487</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.243540305</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.418857</v>
+        <v>0.418837716</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.121516355</v>
+        <v>0.121622651</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.292510384</v>
+        <v>0.292761737</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.15342691</v>
+        <v>0.153731389</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.160013592</v>
+        <v>0.160450703</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.175831293</v>
+        <v>0.17609894</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.21009166</v>
+        <v>0.210219319</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.224209387</v>
+        <v>0.224216193</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215775414</v>
+        <v>0.215638506</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131352191</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131348964</v>
+        <v>0.131350749</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131348235</v>
+        <v>0.131351582</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131344561</v>
+        <v>0.131344947</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131342062</v>
+        <v>0.131346986</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131344613</v>
+        <v>0.131343773</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131347735</v>
+        <v>0.131345689</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131350575</v>
+        <v>0.131343316</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131340902</v>
+        <v>0.131348625</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131346132</v>
+        <v>0.131342133</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.001230305</v>
+        <v>0.000952795</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001236555</v>
+        <v>-0.001250433</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.000805338</v>
+        <v>-0.002764186</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.013973955</v>
+        <v>-0.007463101</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.00163545</v>
+        <v>0.003378261</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.006653814</v>
+        <v>-0.002926708</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.002285036</v>
+        <v>-0.006066855</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.000262706</v>
+        <v>-0.002880086</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.008358809</v>
+        <v>-0.002694488</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.010199848</v>
+        <v>-0.001941914</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.001230305</v>
+        <v>0.000952795</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001236555</v>
+        <v>-0.001250433</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.000805338</v>
+        <v>-0.002764186</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.013973955</v>
+        <v>-0.007463101</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.00163545</v>
+        <v>0.003378261</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.006653814</v>
+        <v>-0.002926708</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.002285036</v>
+        <v>-0.006066855</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>0.000262706</v>
+        <v>-0.002880086</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.008358809</v>
+        <v>-0.002694488</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.010199848</v>
+        <v>-0.001941914</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8845,29 +8845,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.415198238</v>
+        <v>2.415565345</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.872514243</v>
+        <v>0.872635426</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.463203215</v>
+        <v>0.463180853</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.359998431</v>
+        <v>0.360059624</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.234588201</v>
+        <v>0.234627365</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.23889525</v>
+        <v>0.238909524</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193942023</v>
+        <v>0.19395105</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.182721471</v>
+        <v>0.182722678</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8969,33 +8969,33 @@
         <v>0.487077727</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.37243719</v>
+        <v>0.372388023</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.235688185</v>
+        <v>0.235732454</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.235323109</v>
+        <v>0.235381092</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189345224</v>
+        <v>0.18940674</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181064762</v>
+        <v>0.181106091</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135863936</v>
+        <v>0.135879189</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150383903</v>
+        <v>0.150420613</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.13147935</v>
+        <v>0.131481387</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.130722204</v>
+        <v>0.130732468</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4370</v>
+        <v>4300</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,565원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,450원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960782488925288</v>
+        <v>0.1960716811195057</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618929325549621</v>
+        <v>0.05618832844472813</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05880976863799442</v>
+        <v>0.05882390576290762</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04061950044634533</v>
+        <v>0.04064359025618871</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>635.2</v>
+        <v>635.3</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.88</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="32">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249923억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 249920억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 260694억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 260680억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267074억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267048억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276691억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 276655억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 290022억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289980억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 306602억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 306561억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 323220억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 323180억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 338726억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 338688억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352563억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 352527억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249923억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 249920억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 260694억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 260680억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267074억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267048억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276691억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276655억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 290022억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289980억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 306602억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 306561억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 323220억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 323180억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 338726억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 338688억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352563억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352527억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6641,33 +6641,33 @@
         <v>0.243540305</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.418837716</v>
+        <v>0.418818431</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.121622651</v>
+        <v>0.121551787</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.292761737</v>
+        <v>0.292627682</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153731389</v>
+        <v>0.153594373</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.160450703</v>
+        <v>0.16028978</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.17609894</v>
+        <v>0.176015291</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210219319</v>
+        <v>0.21020223</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.224216193</v>
+        <v>0.22421643</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215638506</v>
+        <v>0.215694773</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131352191</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131350749</v>
+        <v>0.131352534</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131351582</v>
+        <v>0.131344085</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131344947</v>
+        <v>0.131345605</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131346986</v>
+        <v>0.13134939</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131343773</v>
+        <v>0.131352061</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131345689</v>
+        <v>0.131349899</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131343316</v>
+        <v>0.13134808</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131348625</v>
+        <v>0.13134264</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131342133</v>
+        <v>0.131346419</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000952795</v>
+        <v>0.000703187</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001250433</v>
+        <v>-0.001435466</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.002764186</v>
+        <v>-0.010877898</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.007463101</v>
+        <v>0.004475735</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.003378261</v>
+        <v>-0.004700865</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.002926708</v>
+        <v>-0.001163893</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.006066855</v>
+        <v>0.005708335</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.002880086</v>
+        <v>-0.001043692</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.002694488</v>
+        <v>-0.009010089000000001</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.001941914</v>
+        <v>-0.000233757</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.000952795</v>
+        <v>0.000703187</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001250433</v>
+        <v>-0.001435466</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.002764186</v>
+        <v>-0.010877898</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.007463101</v>
+        <v>0.004475735</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.003378261</v>
+        <v>-0.004700865</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.002926708</v>
+        <v>-0.001163893</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.006066855</v>
+        <v>0.005708335</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.002880086</v>
+        <v>-0.001043692</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.002694488</v>
+        <v>-0.009010089000000001</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.001941914</v>
+        <v>-0.000233757</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8845,29 +8845,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.415565345</v>
+        <v>2.415198238</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.872635426</v>
+        <v>0.872621735</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.463180853</v>
+        <v>0.463234028</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.360059624</v>
+        <v>0.360048645</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.234627365</v>
+        <v>0.23458998</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.238909524</v>
+        <v>0.238914069</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.19395105</v>
+        <v>0.193954137</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.182722678</v>
+        <v>0.182727086</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8976,26 +8976,26 @@
         <v>0.235732454</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.235381092</v>
+        <v>0.2353521</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.18940674</v>
+        <v>0.189364249</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181106091</v>
+        <v>0.18109708</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135879189</v>
+        <v>0.135888269</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150420613</v>
+        <v>0.150400047</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.131481387</v>
+        <v>0.131478688</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.130732468</v>
+        <v>0.13072021</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960716811195057</v>
+        <v>0.196073140092123</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618832844472813</v>
+        <v>0.05618880371983964</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05882390576290762</v>
+        <v>0.05882998027233148</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04064359025618871</v>
+        <v>0.04064947499608945</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4300</v>
+        <v>4165</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6304,7 +6304,7 @@
         <v>5420</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>4630</v>
+        <v>4650</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4255</v>
+        <v>4125</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4487</v>
+        <v>4433.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4300</v>
+        <v>4165</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.77</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="32">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249920억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 249911억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 260680억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 260624억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267048억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266945억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276655억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 276501억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289980억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289785억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 306561억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 306365억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 323180억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 322988억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 338688억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 338503억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352527억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 352352억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249920억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 249911억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 260680억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 260624억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267048억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266945억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276655억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276501억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289980억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289785억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 306561억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 306365억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 323180억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 322988억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 338688억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 338503억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352527억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352352억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2160,7 +2160,7 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 599억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 598억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2220,7 +2220,7 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 599억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 598억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4165</v>
+        <v>4170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4125</v>
+        <v>3900</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4433.3</v>
+        <v>4395</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.243540305</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.418818431</v>
+        <v>0.418760578</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.121551787</v>
+        <v>0.121321478</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.292627682</v>
+        <v>0.292124975</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153594373</v>
+        <v>0.152939744</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.16028978</v>
+        <v>0.159562322</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.176015291</v>
+        <v>0.175498467</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.21020223</v>
+        <v>0.209946829</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.22421643</v>
+        <v>0.224251307</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215694773</v>
+        <v>0.215909224</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131352191</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131352534</v>
+        <v>0.131344298</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131344085</v>
+        <v>0.131339463</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131345605</v>
+        <v>0.131344832</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.13134939</v>
+        <v>0.131344742</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131352061</v>
+        <v>0.131346048</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131349899</v>
+        <v>0.131340555</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.13134808</v>
+        <v>0.131341172</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.13134264</v>
+        <v>0.131348757</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131346419</v>
+        <v>0.131343514</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000703187</v>
+        <v>0.001884053</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001435466</v>
+        <v>-0.008223794</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.010877898</v>
+        <v>-0.005810914</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.004475735</v>
+        <v>-0.006645001</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.004700865</v>
+        <v>-0.002275409</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.001163893</v>
+        <v>0.004795051</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.005708335</v>
+        <v>-0.011115349</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.001043692</v>
+        <v>0.003558324</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.009010089000000001</v>
+        <v>0.000946873</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000233757</v>
+        <v>-0.008810426</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.000703187</v>
+        <v>0.001884053</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001435466</v>
+        <v>-0.008223794</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.010877898</v>
+        <v>-0.005810914</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>0.004475735</v>
+        <v>-0.006645001</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.004700865</v>
+        <v>-0.002275409</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.001163893</v>
+        <v>0.004795051</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.005708335</v>
+        <v>-0.011115349</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.001043692</v>
+        <v>0.003558324</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.009010089000000001</v>
+        <v>0.000946873</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.000233757</v>
+        <v>-0.008810426</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8845,29 +8845,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.415198238</v>
+        <v>2.414831131</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.872621735</v>
+        <v>0.87228553</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.463234028</v>
+        <v>0.463137345</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.360048645</v>
+        <v>0.359901107</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.23458998</v>
+        <v>0.234582864</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.238914069</v>
+        <v>0.238862138</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193954137</v>
+        <v>0.193939737</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.182727086</v>
+        <v>0.182743363</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8973,29 +8973,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.235732454</v>
+        <v>0.235660803</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.2353521</v>
+        <v>0.235278768</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189364249</v>
+        <v>0.189292588</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.18109708</v>
+        <v>0.181010835</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135888269</v>
+        <v>0.135822068</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150400047</v>
+        <v>0.150358241</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.131478688</v>
+        <v>0.131460142</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.13072021</v>
+        <v>0.130699672</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4165</v>
+        <v>4170</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,340원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.196073140092123</v>
+        <v>0.1960658362658027</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618880371983964</v>
+        <v>0.05618845864731719</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05882998027233148</v>
+        <v>0.05882901958806384</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04064947499608945</v>
+        <v>0.04063749393854074</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>635.3</v>
+        <v>635.2</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249911억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 249909억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 260624억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 260669억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266945억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267036억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276501억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 276636억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289785억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289965억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 306365억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 306540억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 322988억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 323156억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 338503억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 338664억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352352억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 352503억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249911억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 249909억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 260624억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 260669억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266945억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267036억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276501억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276636억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289785억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289965억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 306365억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 306540억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 322988억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 323156억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 338503억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 338664억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352352억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352503억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2160,7 +2160,7 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 598억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 599억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2220,7 +2220,7 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 598억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 599억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4170</v>
+        <v>4160</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4395</v>
+        <v>4351.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6645,29 +6645,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.121321478</v>
+        <v>0.121516355</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.292124975</v>
+        <v>0.292577411</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.152939744</v>
+        <v>0.15350303</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.159562322</v>
+        <v>0.160282724</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.175498467</v>
+        <v>0.175973462</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.209946829</v>
+        <v>0.210158549</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.224251307</v>
+        <v>0.224234185</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215909224</v>
+        <v>0.215669736</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6959,32 +6959,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131339463</v>
+        <v>0.131348235</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131344832</v>
+        <v>0.131350714</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131344742</v>
+        <v>0.131346593</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131346048</v>
+        <v>0.131346501</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131340555</v>
+        <v>0.131345288</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131341172</v>
+        <v>0.131347217</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131348757</v>
+        <v>0.131340355</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131343514</v>
+        <v>0.131345642</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.001884053</v>
+        <v>0.001833055</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.008223794</v>
+        <v>-0.008674167</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005810914</v>
+        <v>-0.000456501</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.006645001</v>
+        <v>0.004455161</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002275409</v>
+        <v>-0.003165412</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.004795051</v>
+        <v>-0.010027495</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.011115349</v>
+        <v>-0.003732628</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.003558324</v>
+        <v>-0.001002801</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.000946873</v>
+        <v>-0.009596225999999999</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.008810426</v>
+        <v>-0.001329128</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.001884053</v>
+        <v>0.001833055</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.008223794</v>
+        <v>-0.008674167</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.005810914</v>
+        <v>-0.000456501</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.006645001</v>
+        <v>0.004455161</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.002275409</v>
+        <v>-0.003165412</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.004795051</v>
+        <v>-0.010027495</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.011115349</v>
+        <v>-0.003732628</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>0.003558324</v>
+        <v>-0.001002801</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.000946873</v>
+        <v>-0.009596225999999999</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.008810426</v>
+        <v>-0.001329128</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8845,29 +8845,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.414831131</v>
+        <v>2.415198238</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.87228553</v>
+        <v>0.872514243</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.463137345</v>
+        <v>0.463203215</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.359901107</v>
+        <v>0.360076896</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.234582864</v>
+        <v>0.234603513</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.238862138</v>
+        <v>0.238901869</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193939737</v>
+        <v>0.193946252</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.182743363</v>
+        <v>0.182722836</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8973,29 +8973,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.235660803</v>
+        <v>0.235696629</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.235278768</v>
+        <v>0.235358924</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189292588</v>
+        <v>0.189368693</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181010835</v>
+        <v>0.181080921</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135822068</v>
+        <v>0.135876103</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150358241</v>
+        <v>0.150391975</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.131460142</v>
+        <v>0.131485412</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.130699672</v>
+        <v>0.130714818</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4170</v>
+        <v>4160</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,340원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,125원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960658362658027</v>
+        <v>0.1960729573794901</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618845864731719</v>
+        <v>0.05618807853910995</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05882901958806384</v>
+        <v>0.05880521700434227</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04063749393854074</v>
+        <v>0.04061374172750618</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 249909억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 250205억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 260669억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 261148억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267036억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267513억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276636억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 276969억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289965억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289749억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 306540억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 305817억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 323156억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 322084억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 338664억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 337406억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352503억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 351223억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 249909억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 250205억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 260669억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261148억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267036억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267513억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276636억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276969억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289965억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289749억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 306540억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 305817억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 323156억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 322084억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 338664억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 337406억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352503억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 351223억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4160</v>
+        <v>4075</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4351.9</v>
+        <v>4260.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.243540305</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.418760578</v>
+        <v>0.420438329</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.121516355</v>
+        <v>0.12357142</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.292577411</v>
+        <v>0.294889864</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.15350303</v>
+        <v>0.154888408</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.160282724</v>
+        <v>0.158043363</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.175973462</v>
+        <v>0.171047445</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210158549</v>
+        <v>0.203985765</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.224234185</v>
+        <v>0.21821777</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215669736</v>
+        <v>0.212162067</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131352191</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131344298</v>
+        <v>0.131352078</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131348235</v>
+        <v>0.131344507</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131350714</v>
+        <v>0.131349078</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131346593</v>
+        <v>0.131347219</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131346501</v>
+        <v>0.131351263</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131345288</v>
+        <v>0.131346861</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131347217</v>
+        <v>0.131344182</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131340355</v>
+        <v>0.131343736</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131345642</v>
+        <v>0.131350646</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.001833055</v>
+        <v>0.002125557</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.008674167</v>
+        <v>-0.001561699</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.000456501</v>
+        <v>0.002039303</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.004455161</v>
+        <v>-0.006989427</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.003165412</v>
+        <v>-0.00087739</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.010027495</v>
+        <v>0.003077487</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.003732628</v>
+        <v>-0.001667316</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.001002801</v>
+        <v>-0.005256145</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.009596225999999999</v>
+        <v>0.000615886</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.001329128</v>
+        <v>0.002876809</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.001833055</v>
+        <v>0.002125557</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.008674167</v>
+        <v>-0.001561699</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.000456501</v>
+        <v>0.002039303</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>0.004455161</v>
+        <v>-0.006989427</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.003165412</v>
+        <v>-0.00087739</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.010027495</v>
+        <v>0.003077487</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.003732628</v>
+        <v>-0.001667316</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.001002801</v>
+        <v>-0.005256145</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.009596225999999999</v>
+        <v>0.000615886</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.001329128</v>
+        <v>0.002876809</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8841,33 +8841,33 @@
         <v>-0.578709269</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-1.561649485</v>
+        <v>-1.563505155</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.415198238</v>
+        <v>2.411635565</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.872514243</v>
+        <v>0.8722651219999999</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.463203215</v>
+        <v>0.462794295</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.360076896</v>
+        <v>0.359140038</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.234603513</v>
+        <v>0.233814504</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.238901869</v>
+        <v>0.238031853</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193946252</v>
+        <v>0.193284919</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.182722836</v>
+        <v>0.182226297</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8969,33 +8969,33 @@
         <v>0.487077727</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.372388023</v>
+        <v>0.372830523</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.235696629</v>
+        <v>0.23608624</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.235358924</v>
+        <v>0.235614533</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189368693</v>
+        <v>0.189443324</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.181080921</v>
+        <v>0.180798423</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.135876103</v>
+        <v>0.13548484</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.150391975</v>
+        <v>0.149872815</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.131485412</v>
+        <v>0.131029103</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.130714818</v>
+        <v>0.130332048</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4160</v>
+        <v>4075</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,125원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,920원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960729573794901</v>
+        <v>0.1960652805723228</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05618807853910995</v>
+        <v>0.05619205458571477</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05880521700434227</v>
+        <v>0.0588246956391039</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04061374172750618</v>
+        <v>0.04063123843639461</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>635.2</v>
+        <v>636</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.55</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="32">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="33">
@@ -41998,7 +41998,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2089</v>
+        <v>0.2091</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/014940_model.xlsx
+++ b/argus/kship/models/014940_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 250205억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 250427억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261148억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 261550억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267513억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267954억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276969억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 277338억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 289749억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289742억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 305817억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 305423억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 322084억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 321423억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 337406억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 336603억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 351223억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 350402억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 250205억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 250427억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261148억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261550억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267513억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267954억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276969억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 277338억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 289749억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289742억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 305817억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 305423억 × 비례계수 0.0110 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 322084억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 321423억 × 비례계수 0.0110 × 계절비중 Q2 0.263(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 337406억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336603억 × 비례계수 0.0110 × 계절비중 Q3 0.249(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 351223억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 350402억 × 비례계수 0.0110 × 계절비중 Q4 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.95, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2148,13 +2148,13 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 426억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 427억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 507억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 508억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2178,7 +2178,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 885억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 884억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2208,13 +2208,13 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 426억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 427억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 507억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 508억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2238,7 +2238,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 885억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 884억 × 5.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 250억 × 4.06%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5245,35 +5245,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5364,35 +5364,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5483,35 +5483,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5602,35 +5602,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5721,35 +5721,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5840,35 +5840,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5959,35 +5959,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6078,35 +6078,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6213,7 +6213,7 @@
         <v>4450</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4075</v>
+        <v>3615</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6395,7 +6395,7 @@
         <v>3530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3800</v>
+        <v>3590</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4589.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4260.5</v>
+        <v>4108.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6641,33 +6641,33 @@
         <v>0.243540305</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.420438329</v>
+        <v>0.421691821</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.12357142</v>
+        <v>0.125307595</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.294889864</v>
+        <v>0.297017991</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.154888408</v>
+        <v>0.156441251</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.158043363</v>
+        <v>0.156995198</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.171047445</v>
+        <v>0.167729341</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.203985765</v>
+        <v>0.199542647</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.21821777</v>
+        <v>0.21368579</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.212162067</v>
+        <v>0.209365035</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,39 +6952,39 @@
         <v>0.131352191</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.131352078</v>
+        <v>0.131344782</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.131344507</v>
+        <v>0.131346526</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.131349078</v>
+        <v>0.131340275</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.131347219</v>
+        <v>0.131341987</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.131351263</v>
+        <v>0.131342619</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.131346861</v>
+        <v>0.131341593</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.131344182</v>
+        <v>0.131345116</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.131343736</v>
+        <v>0.131342604</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.131350646</v>
+        <v>0.131347306</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8454,36 +8454,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.002125557</v>
+        <v>0.001592233</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001561699</v>
+        <v>-0.007720879</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.002039303</v>
+        <v>-0.002786613</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.006989427</v>
+        <v>-0.006530376</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.00087739</v>
+        <v>-0.002667997</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.003077487</v>
+        <v>0.000113848</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.001667316</v>
+        <v>-0.010626899</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.005256145</v>
+        <v>-0.00190886</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.000615886</v>
+        <v>-0.00030674</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.002876809</v>
+        <v>0.005224503</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.002125557</v>
+        <v>0.001592233</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001561699</v>
+        <v>-0.007720879</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.002039303</v>
+        <v>-0.002786613</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>-0.006989427</v>
+        <v>-0.006530376</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.00087739</v>
+        <v>-0.002667997</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.003077487</v>
+        <v>0.000113848</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.001667316</v>
+        <v>-0.010626899</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.005256145</v>
+        <v>-0.00190886</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.000615886</v>
+        <v>-0.00030674</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.002876809</v>
+        <v>0.005224503</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8841,33 +8841,33 @@
         <v>-0.578709269</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-1.563505155</v>
+        <v>-1.564948454</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>2.411635565</v>
+        <v>2.409489051</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.8722651219999999</v>
+        <v>0.871976022</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.462794295</v>
+        <v>0.462602928</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.359140038</v>
+        <v>0.358550317</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.233814504</v>
+        <v>0.2332729</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.238031853</v>
+        <v>0.237381869</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.193284919</v>
+        <v>0.192803802</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.182226297</v>
+        <v>0.181844052</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -8969,33 +8969,33 @@
         <v>0.487077727</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.372830523</v>
+        <v>0.373174689</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.23608624</v>
+        <v>0.236385119</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.235614533</v>
+        <v>0.23590397</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.189443324</v>
+        <v>0.189563465</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.180798423</v>
+        <v>0.180668545</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.13548484</v>
+        <v>0.135220808</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.149872815</v>
+        <v>0.149506202</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.131029103</v>
+        <v>0.130713272</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.130332048</v>
+        <v>0.130064111</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>4075</v>
+        <v>3615</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,920원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,810원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1960652805723228</v>
+        <v>0.196074776806516</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05619205458571477</v>
+        <v>0.05618846826003943</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0588246956391039</v>
+        <v>0.05883730330022324</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.04063123843639461</v>
+        <v>0.04063308775371197</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41958,7 +41958,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>636</v>
+        <v>636.6</v>
       </c>
     </row>
     <row r="30">
@@ -41978,7 +41978,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.41</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="32">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="33">
@@ -41998,7 +41998,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2091</v>
+        <v>0.2093</v>
       </c>
     </row>
     <row r="34">
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="35">
